--- a/data/raw/inventory/Week 24/Audio_Array/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 24/Audio_Array/Vendor SOH (SP-API).xlsx
@@ -518,12 +518,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,25 +533,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2164.7070972</v>
+        <v>1107.780080664706</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -563,30 +563,32 @@
         <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>30555.39</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -596,25 +598,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2021.262651</v>
+        <v>2335.8554064</v>
       </c>
       <c r="I3" t="n">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -626,32 +628,32 @@
         <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>728802.37</v>
+        <v>27961.31</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,25 +663,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1291.959696295941</v>
+        <v>7722.439199999999</v>
       </c>
       <c r="I4" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -691,32 +693,32 @@
         <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>143645.51</v>
+        <v>155003.82</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -726,7 +728,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -736,15 +738,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>13162.63420323</v>
+        <v>5808.86204274</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -756,32 +758,32 @@
         <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>69917.96000000001</v>
+        <v>58728.55</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -791,25 +793,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>1679.60406096</v>
+        <v>2934.090945</v>
       </c>
       <c r="I6" t="n">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -824,29 +826,29 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>445411.43</v>
+        <v>48808.97</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -856,25 +858,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>847.6262729999999</v>
+        <v>708</v>
       </c>
       <c r="I7" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -886,32 +888,32 @@
         <v>24</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="N7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>111605.33</v>
+        <v>959.1900000000001</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -921,25 +923,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Microphone dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2664.193308210882</v>
+        <v>1499.646483</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -951,30 +953,32 @@
         <v>24</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>373142.05</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -984,25 +988,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>7722.439199999999</v>
+        <v>521.6161679999999</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1014,32 +1018,32 @@
         <v>24</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>155003.82</v>
+        <v>19404.38</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1049,25 +1053,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>179.9635942941177</v>
+        <v>2021.262651</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1079,32 +1083,32 @@
         <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P10" t="n">
-        <v>20983.81</v>
+        <v>667707.7</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1114,25 +1118,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>4486.010979600001</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I11" t="n">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1144,32 +1148,32 @@
         <v>24</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1497679</v>
+        <v>12468.08</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1179,25 +1183,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>RGB USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>4119.760313999999</v>
+        <v>3196.1775</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1209,32 +1213,32 @@
         <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>154506.81</v>
+        <v>1683.77</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1244,25 +1248,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>2975.579697881559</v>
+        <v>2261.3068296</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1274,32 +1278,32 @@
         <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>131914.68</v>
+        <v>27961.31</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1309,25 +1313,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>5118.2854</v>
+        <v>612.8989974</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1339,32 +1343,32 @@
         <v>24</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>120811.9</v>
+        <v>142266.22</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1374,25 +1378,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>260.808084</v>
+        <v>4986.467599999999</v>
       </c>
       <c r="I15" t="n">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1404,32 +1408,32 @@
         <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>562</v>
+        <v>62</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>49916.44</v>
+        <v>284412.39</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1439,25 +1443,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>326.010105</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1469,32 +1473,32 @@
         <v>24</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>22400.09</v>
+        <v>59175.89</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1504,7 +1508,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1514,15 +1518,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>2458.088208</v>
+        <v>2173.4007</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1534,32 +1538,32 @@
         <v>24</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>30967.88</v>
+        <v>65555</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1569,25 +1573,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1201.7320128</v>
+        <v>169.5252546</v>
       </c>
       <c r="I18" t="n">
-        <v>460</v>
+        <v>113</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1599,32 +1603,32 @@
         <v>24</v>
       </c>
       <c r="M18" t="n">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>680075.99</v>
+        <v>46485.87</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1634,25 +1638,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>12112.09532316</v>
+        <v>2179.9269789525</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1664,32 +1668,32 @@
         <v>24</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>47194.42</v>
+        <v>87344.95</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1699,25 +1703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Single UHF Wireless Microphone With Receiver</t>
+          <t>KB-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1825.656588</v>
+        <v>2630.5268</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1729,32 +1733,32 @@
         <v>24</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>35230.28</v>
+        <v>3775.02</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1764,25 +1768,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>3358.8228</v>
+        <v>3277.450944</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1794,32 +1798,32 @@
         <v>24</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>5033.59</v>
+        <v>73753.14</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,25 +1833,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1700.734990628047</v>
+        <v>1291.959696295941</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1859,32 +1863,32 @@
         <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>17187.48</v>
+        <v>141894.35</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA76722</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0BLKDC4PP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1894,25 +1898,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1544.91011775</v>
+        <v>1642.572937873306</v>
       </c>
       <c r="I23" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1924,20 +1928,18 @@
         <v>24</v>
       </c>
       <c r="M23" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>29</v>
-      </c>
-      <c r="P23" t="n">
-        <v>456671.33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2002,19 +2004,19 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2024,25 +2026,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>874.2436631991176</v>
+        <v>4859.948</v>
       </c>
       <c r="I25" t="n">
-        <v>199</v>
+        <v>12</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2054,32 +2056,32 @@
         <v>24</v>
       </c>
       <c r="M25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>12</v>
       </c>
       <c r="O25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>212978.15</v>
+        <v>82498.16</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA77010</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2089,25 +2091,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI-04 Black</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2426.920291998617</v>
+        <v>260.808084</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2119,30 +2121,32 @@
         <v>24</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="P26" t="n">
+        <v>45378.58</v>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2152,25 +2156,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Quad UHF Wireless Microphone With Receiver Box</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>6259.394015999999</v>
+        <v>3317.4116676</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2182,32 +2186,32 @@
         <v>24</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>118505.16</v>
+        <v>88433.71000000001</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79844</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>PB-08 (AM-C1 + AI-04)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2227,15 +2231,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UB-03</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>5619.632</v>
+        <v>3358.8228</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2247,32 +2251,32 @@
         <v>24</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>145423.97</v>
+        <v>5033.59</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2282,25 +2286,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Dual UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1043.232336</v>
+        <v>4694.545512</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2312,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2320,22 +2324,24 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>89138.53999999999</v>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2345,25 +2351,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>130.404042</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2375,32 +2381,32 @@
         <v>24</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>10817.99</v>
+        <v>142621.67</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA75680</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2410,25 +2416,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AM-C6</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1815.59502123</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2440,32 +2446,30 @@
         <v>24</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
-      </c>
-      <c r="P31" t="n">
-        <v>12598.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2475,25 +2479,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>3129.697008</v>
+        <v>2311.522194589411</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2505,32 +2509,32 @@
         <v>24</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>61869.39</v>
+        <v>81298.17999999999</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2540,25 +2544,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>GB-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>1499.646483</v>
+        <v>4630.8156</v>
       </c>
       <c r="I33" t="n">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2570,32 +2574,32 @@
         <v>24</v>
       </c>
       <c r="M33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>377582.81</v>
+        <v>47190.19</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2615,15 +2619,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>3425.8468</v>
+        <v>4841.8232</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2638,29 +2642,29 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>36703.48</v>
+        <v>118574.49</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2670,25 +2674,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>2021.262651</v>
+        <v>920.65253652</v>
       </c>
       <c r="I35" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2700,32 +2704,32 @@
         <v>24</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>95048.94</v>
+        <v>77045.64999999999</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2735,25 +2739,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>2360.3131602</v>
+        <v>3065.101673616</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2765,32 +2769,32 @@
         <v>24</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="N36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>37258.73</v>
+        <v>58725.08</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2800,25 +2804,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>827.5708984229998</v>
+        <v>1700.734990628047</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2830,32 +2834,32 @@
         <v>24</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2014.34</v>
+        <v>17187.48</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2865,25 +2869,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>5118.2854</v>
+        <v>1544.91011775</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2895,32 +2899,32 @@
         <v>24</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>197</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="P38" t="n">
-        <v>36704.9</v>
+        <v>442526.65</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2930,25 +2934,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1159.29193338</v>
+        <v>4696.526757959999</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2960,7 +2964,7 @@
         <v>24</v>
       </c>
       <c r="M39" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2969,23 +2973,23 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1481.65</v>
+        <v>53134.2</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2995,25 +2999,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1043.232336</v>
+        <v>871.9473036705882</v>
       </c>
       <c r="I40" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3025,32 +3029,32 @@
         <v>24</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="N40" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P40" t="n">
-        <v>72127.38</v>
+        <v>37462.57</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3060,25 +3064,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>3998.590893</v>
+        <v>4889.153</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3090,32 +3094,32 @@
         <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>68163.60000000001</v>
+        <v>39150.73</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3125,25 +3129,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>2973.2121576</v>
+        <v>13162.63420323</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3155,32 +3159,32 @@
         <v>24</v>
       </c>
       <c r="M42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>70466.07000000001</v>
+        <v>69917.96000000001</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3190,25 +3194,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1722.835557825</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I43" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3220,32 +3224,32 @@
         <v>24</v>
       </c>
       <c r="M43" t="n">
-        <v>259</v>
+        <v>32</v>
       </c>
       <c r="N43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>163343.96</v>
+        <v>1481.65</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3265,15 +3269,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>4934.296426588235</v>
+        <v>1043.232336</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3285,32 +3289,32 @@
         <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>24327.52</v>
+        <v>69298.84</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3320,25 +3324,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>4277.252577599999</v>
+        <v>659.7098370441175</v>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3350,32 +3354,32 @@
         <v>24</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P45" t="n">
-        <v>14680.56</v>
+        <v>36581.89</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3385,25 +3389,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wireless Mic with Charging Case</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>11761.9332</v>
+        <v>4180.2798</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3415,32 +3419,32 @@
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6031.48</v>
+        <v>49777.93</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3450,25 +3454,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>3277.450944</v>
+        <v>1092.483648</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3480,32 +3484,32 @@
         <v>24</v>
       </c>
       <c r="M47" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>73753.14</v>
+        <v>41823.6</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3515,25 +3519,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1956.06063</v>
+        <v>503.35960212</v>
       </c>
       <c r="I48" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3545,32 +3549,32 @@
         <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>108697.64</v>
+        <v>41244.99</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3580,25 +3584,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>4859.948</v>
+        <v>3140.890488</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3613,29 +3617,29 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>82498.16</v>
+        <v>317521.06</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3645,25 +3649,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>2051.276637829411</v>
+        <v>1679.6</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3675,32 +3679,32 @@
         <v>24</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
       <c r="P50" t="n">
-        <v>2050.99</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3710,25 +3714,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>3221.74692</v>
+        <v>1956.06063</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3740,32 +3744,32 @@
         <v>24</v>
       </c>
       <c r="M51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P51" t="n">
-        <v>46560.22</v>
+        <v>111284.01</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3775,25 +3779,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>GB-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>534.6565721999999</v>
+        <v>3909.104</v>
       </c>
       <c r="I52" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3808,29 +3812,29 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>12468.08</v>
+        <v>92490.47</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3840,25 +3844,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1984.74951924</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3870,32 +3874,32 @@
         <v>24</v>
       </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>26249.26</v>
+        <v>74082.34</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3905,25 +3909,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>3140.890488</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I54" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3935,32 +3939,32 @@
         <v>24</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>317521.06</v>
+        <v>51248.05</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3970,25 +3974,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GB-02</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1983.58</v>
+        <v>756.3434436</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4000,32 +4004,32 @@
         <v>24</v>
       </c>
       <c r="M55" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>30058.96</v>
+        <v>48229.06</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4035,25 +4039,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>2119.874127397059</v>
+        <v>7169.514799999999</v>
       </c>
       <c r="I56" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4065,20 +4069,20 @@
         <v>24</v>
       </c>
       <c r="M56" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>93951.10000000001</v>
+        <v>81102.49000000001</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4143,19 +4147,19 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4165,25 +4169,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>659.7098370441175</v>
+        <v>1679.60406096</v>
       </c>
       <c r="I58" t="n">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4195,32 +4199,32 @@
         <v>24</v>
       </c>
       <c r="M58" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="O58" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>36581.89</v>
+        <v>445411.43</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4230,25 +4234,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AM-W48 / AM-S6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Party Speaker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>Dual 12" 160W Bluetooth Party Speaker</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>503.35960212</v>
+        <v>13607.288</v>
       </c>
       <c r="I59" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4260,32 +4264,30 @@
         <v>24</v>
       </c>
       <c r="M59" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="P59" t="n">
-        <v>42204.17</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA75680</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4295,25 +4297,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>AM-C6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>2585.9936</v>
+        <v>1815.59502123</v>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4325,32 +4327,32 @@
         <v>24</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P60" t="n">
-        <v>46140.06</v>
+        <v>12598.26</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4360,25 +4362,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>614.5220519999999</v>
+        <v>1693.3496544</v>
       </c>
       <c r="I61" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4390,32 +4392,32 @@
         <v>24</v>
       </c>
       <c r="M61" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>107628.43</v>
+        <v>60217.88</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4425,25 +4427,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RGB USB Microphone Kit - Tripod</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>3196.1775</v>
+        <v>326.010105</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4455,32 +4457,32 @@
         <v>24</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1683.77</v>
+        <v>21828.64</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4490,25 +4492,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>2973.2121576</v>
+        <v>2458.088208</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4520,32 +4522,32 @@
         <v>24</v>
       </c>
       <c r="M63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" t="n">
-        <v>51248.05</v>
+        <v>30967.88</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4555,25 +4557,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>04 channels Mixer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>2870.1202068</v>
+        <v>1948.404289679999</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4585,7 +4587,7 @@
         <v>24</v>
       </c>
       <c r="M64" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -4594,23 +4596,23 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>73402.06</v>
+        <v>40894.6</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4620,25 +4622,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wireless Conference Microphone</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>2738.484882</v>
+        <v>5619.632</v>
       </c>
       <c r="I65" t="n">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4650,32 +4652,32 @@
         <v>24</v>
       </c>
       <c r="M65" t="n">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>612913.37</v>
+        <v>136334.97</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA76727</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4685,25 +4687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AM-C24</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>GB-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1676.644024574118</v>
+        <v>1983.58</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4715,32 +4717,32 @@
         <v>24</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1074.36</v>
+        <v>30058.96</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4750,25 +4752,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>6 channels mixer</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>4696.526757959999</v>
+        <v>2021.262651</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4780,32 +4782,32 @@
         <v>24</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67" t="n">
-        <v>53134.2</v>
+        <v>97617.83</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4815,25 +4817,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>2263.0394</v>
+        <v>905.00405148</v>
       </c>
       <c r="I68" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4848,29 +4850,29 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>39426.9</v>
+        <v>67344.32000000001</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4880,25 +4882,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1107.780080664706</v>
+        <v>1201.7320128</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4910,32 +4912,32 @@
         <v>24</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="N69" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>32089.83</v>
+        <v>665259.52</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4945,25 +4947,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>6152.0362</v>
+        <v>598.3056269558823</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4975,32 +4977,32 @@
         <v>24</v>
       </c>
       <c r="M70" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P70" t="n">
-        <v>8809.32</v>
+        <v>24277.86</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5010,25 +5012,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>7169.514799999999</v>
+        <v>2975.579697881559</v>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5040,32 +5042,32 @@
         <v>24</v>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P71" t="n">
-        <v>81102.49000000001</v>
+        <v>131914.68</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5075,25 +5077,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>4180.2798</v>
+        <v>2167.31517804</v>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5105,32 +5107,32 @@
         <v>24</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P72" t="n">
-        <v>49777.93</v>
+        <v>57244.21</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA75678</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5140,7 +5142,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AA-01</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5155,10 +5157,10 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>1224.499030661912</v>
+        <v>130.404042</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5170,32 +5172,32 @@
         <v>24</v>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>30821.61</v>
+        <v>10817.99</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5205,25 +5207,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1566.15254442</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I74" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5235,32 +5237,32 @@
         <v>24</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="N74" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>124951.01</v>
+        <v>145995.33</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5270,25 +5272,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>4889.153</v>
+        <v>1043.232336</v>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5300,32 +5302,32 @@
         <v>24</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>39150.73</v>
+        <v>31199.36</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5335,7 +5337,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5350,10 +5352,10 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>2167.31517804</v>
+        <v>2360.3131602</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5365,32 +5367,32 @@
         <v>24</v>
       </c>
       <c r="M76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O76" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>57244.21</v>
+        <v>40124.79</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5400,25 +5402,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>2857.758705882353</v>
+        <v>827.5708984229998</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5433,29 +5435,29 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1885.92</v>
+        <v>2014.34</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5465,25 +5467,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>2934.090945</v>
+        <v>2585.9936</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5495,32 +5497,32 @@
         <v>24</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>48808.97</v>
+        <v>50334.62</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA76722</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0BLKDC4PP</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5530,7 +5532,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-C19</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5540,15 +5542,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1642.572937873306</v>
+        <v>1475.964687829412</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1330</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5560,30 +5562,32 @@
         <v>24</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2511701.35</v>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5593,25 +5597,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>1722.835557825</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5623,32 +5627,32 @@
         <v>24</v>
       </c>
       <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="N80" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>3</v>
-      </c>
       <c r="P80" t="n">
-        <v>59175.89</v>
+        <v>79701.3</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5658,25 +5662,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KB-01</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>2630.5268</v>
+        <v>1330.281037275</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5688,32 +5692,32 @@
         <v>24</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P81" t="n">
-        <v>3775.02</v>
+        <v>41698.28</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5723,25 +5727,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>756.3434436</v>
+        <v>3835.413</v>
       </c>
       <c r="I82" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5756,29 +5760,27 @@
         <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>2</v>
-      </c>
-      <c r="P82" t="n">
-        <v>49303.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5788,25 +5790,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>5808.86204274</v>
+        <v>1305.459898830882</v>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5818,32 +5820,32 @@
         <v>24</v>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
         <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>58728.55</v>
+        <v>14911.51</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5853,7 +5855,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5863,15 +5865,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Tripod</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>734.122339149</v>
+        <v>1499.646483</v>
       </c>
       <c r="I84" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5883,32 +5885,32 @@
         <v>24</v>
       </c>
       <c r="M84" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="N84" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>61065.31</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5918,25 +5920,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>912.8282939999998</v>
+        <v>1956.963080117647</v>
       </c>
       <c r="I85" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5948,32 +5950,32 @@
         <v>24</v>
       </c>
       <c r="M85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>12458.18</v>
+        <v>38167.64</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5983,25 +5985,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>2335.8554064</v>
+        <v>3425.8468</v>
       </c>
       <c r="I86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6013,32 +6015,32 @@
         <v>24</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>27961.31</v>
+        <v>26216.77</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA76728</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6048,25 +6050,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AM-C25</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>2157.615343358823</v>
+        <v>1984.74951924</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6078,30 +6080,32 @@
         <v>24</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>29115.32</v>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6111,25 +6115,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AM-W48 / AM-S6</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Party Speaker</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dual 12" 160W Bluetooth Party Speaker</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>13607.288</v>
+        <v>280.0829144294117</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6141,30 +6145,32 @@
         <v>24</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="P88" t="n">
+        <v>46190.12</v>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6174,25 +6180,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GB-05</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>3909.104</v>
+        <v>847.6262729999999</v>
       </c>
       <c r="I89" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6204,32 +6210,32 @@
         <v>24</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N89" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P89" t="n">
-        <v>92490.47</v>
+        <v>101820.92</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6239,25 +6245,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>1679.6</v>
+        <v>1960.237563966397</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6269,32 +6275,32 @@
         <v>24</v>
       </c>
       <c r="M90" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>223131.07</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6304,25 +6310,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver Box</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>4694.545512</v>
+        <v>179.9635942941177</v>
       </c>
       <c r="I91" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -6334,32 +6340,32 @@
         <v>24</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>89138.53999999999</v>
+        <v>21316.88</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6369,25 +6375,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>534.6565721999999</v>
+        <v>4486.010979600001</v>
       </c>
       <c r="I92" t="n">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6399,32 +6405,32 @@
         <v>24</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P92" t="n">
-        <v>10805.67</v>
+        <v>1497539.16</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6434,25 +6440,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>1330.281037275</v>
+        <v>1566.15254442</v>
       </c>
       <c r="I93" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6464,32 +6470,32 @@
         <v>24</v>
       </c>
       <c r="M93" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
+        <v>54</v>
+      </c>
+      <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="O93" t="n">
-        <v>3</v>
-      </c>
       <c r="P93" t="n">
-        <v>43366.22</v>
+        <v>127308.58</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA76728</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6499,7 +6505,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>AM-C25</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6509,12 +6515,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>3835.413</v>
+        <v>2157.615343358823</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -6529,7 +6535,7 @@
         <v>24</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -6540,19 +6546,19 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6562,25 +6568,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>3317.4116676</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I95" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6598,26 +6604,26 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>99968.53999999999</v>
+        <v>12458.18</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6627,25 +6633,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>2261.3068296</v>
+        <v>1194.50102472</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6657,32 +6663,32 @@
         <v>24</v>
       </c>
       <c r="M96" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P96" t="n">
-        <v>27961.31</v>
+        <v>73812.85000000001</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6692,25 +6698,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>477.9615959999999</v>
+        <v>4934.296426588235</v>
       </c>
       <c r="I97" t="n">
-        <v>234</v>
+        <v>7</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6722,32 +6728,32 @@
         <v>24</v>
       </c>
       <c r="M97" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>216033.7</v>
+        <v>24327.52</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6757,25 +6763,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>1092.483648</v>
+        <v>3221.74692</v>
       </c>
       <c r="I98" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6787,32 +6793,32 @@
         <v>24</v>
       </c>
       <c r="M98" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P98" t="n">
-        <v>80549.16</v>
+        <v>46560.22</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6822,25 +6828,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone dynamic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Mobile Microphone</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1043.232336</v>
+        <v>2664.193308210882</v>
       </c>
       <c r="I99" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6852,32 +6858,30 @@
         <v>24</v>
       </c>
       <c r="M99" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" t="n">
-        <v>32445.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6887,7 +6891,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6897,15 +6901,15 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>GB-04</t>
+          <t>PB-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>4630.8156</v>
+        <v>6152.0362</v>
       </c>
       <c r="I100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6917,32 +6921,32 @@
         <v>24</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N100" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>47190.19</v>
+        <v>8809.32</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6952,25 +6956,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>871.9473036705882</v>
+        <v>4042.525302</v>
       </c>
       <c r="I101" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6982,32 +6986,32 @@
         <v>24</v>
       </c>
       <c r="M101" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O101" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>40864.54</v>
+        <v>115246.23</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7017,25 +7021,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>1304.04042</v>
+        <v>2738.484882</v>
       </c>
       <c r="I102" t="n">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7047,32 +7051,32 @@
         <v>24</v>
       </c>
       <c r="M102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O102" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="P102" t="n">
-        <v>233933.92</v>
+        <v>124127.54</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7082,25 +7086,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>169.5252546</v>
+        <v>3748.5845172</v>
       </c>
       <c r="I103" t="n">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7112,32 +7116,32 @@
         <v>24</v>
       </c>
       <c r="M103" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P103" t="n">
-        <v>47723.47</v>
+        <v>1184015.05</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7147,25 +7151,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>1956.963080117647</v>
+        <v>1043.232336</v>
       </c>
       <c r="I104" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7177,32 +7181,30 @@
         <v>24</v>
       </c>
       <c r="M104" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="P104" t="n">
-        <v>41103.61</v>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7212,25 +7214,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>2165.574481998618</v>
+        <v>2870.1202068</v>
       </c>
       <c r="I105" t="n">
-        <v>791</v>
+        <v>20</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7242,32 +7244,32 @@
         <v>24</v>
       </c>
       <c r="M105" t="n">
-        <v>380</v>
+        <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>2759035.41</v>
+        <v>69906.72</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7277,25 +7279,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>678.1010183999999</v>
+        <v>2051.276637829411</v>
       </c>
       <c r="I106" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7307,32 +7309,32 @@
         <v>24</v>
       </c>
       <c r="M106" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>79532.19</v>
+        <v>2050.99</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7342,25 +7344,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>4841.8232</v>
+        <v>1304.04042</v>
       </c>
       <c r="I107" t="n">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -7372,32 +7374,32 @@
         <v>24</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N107" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P107" t="n">
-        <v>118574.49</v>
+        <v>261211.92</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7407,25 +7409,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>1235.473403164659</v>
+        <v>614.5220519999999</v>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -7437,32 +7439,32 @@
         <v>24</v>
       </c>
       <c r="M108" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="N108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P108" t="n">
-        <v>4669.47</v>
+        <v>101105.5</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7472,25 +7474,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>1499.646483</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7502,32 +7504,32 @@
         <v>24</v>
       </c>
       <c r="M109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>22424.73</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA75678</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7537,25 +7539,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AA-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>5836.846399999999</v>
+        <v>1224.499030661912</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7567,32 +7569,32 @@
         <v>24</v>
       </c>
       <c r="M110" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P110" t="n">
-        <v>9089</v>
+        <v>30821.61</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7602,25 +7604,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1948.404289679999</v>
+        <v>1092.483648</v>
       </c>
       <c r="I111" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7632,32 +7634,32 @@
         <v>24</v>
       </c>
       <c r="M111" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P111" t="n">
-        <v>37748.86</v>
+        <v>77451.12</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7667,7 +7669,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7677,15 +7679,15 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>2280.5034</v>
+        <v>5118.2854</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7697,32 +7699,32 @@
         <v>24</v>
       </c>
       <c r="M112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>36704.9</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7732,7 +7734,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7747,10 +7749,10 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>1159.29193338</v>
+        <v>2803.686903</v>
       </c>
       <c r="I113" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7762,32 +7764,32 @@
         <v>24</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>74082.34</v>
+        <v>2460.51</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7797,22 +7799,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>2803.686903</v>
+        <v>1828.2802</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -7827,30 +7829,32 @@
         <v>24</v>
       </c>
       <c r="M114" t="n">
+        <v>50</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
         <v>6</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7860,25 +7864,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>9527.5088</v>
+        <v>678.1010183999999</v>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7890,32 +7894,32 @@
         <v>24</v>
       </c>
       <c r="M115" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P115" t="n">
-        <v>58031.42</v>
+        <v>79532.19</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7925,25 +7929,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Dual UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>2179.9269789525</v>
+        <v>3129.697008</v>
       </c>
       <c r="I116" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7955,32 +7959,32 @@
         <v>24</v>
       </c>
       <c r="M116" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>87344.95</v>
+        <v>61869.39</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7990,25 +7994,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1092.483648</v>
+        <v>12112.09532316</v>
       </c>
       <c r="I117" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8020,32 +8024,32 @@
         <v>24</v>
       </c>
       <c r="M117" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>43372.63</v>
+        <v>47194.42</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8055,25 +8059,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Conference Microphone</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>2164.7070972</v>
+        <v>2738.484882</v>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8085,32 +8089,32 @@
         <v>24</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P118" t="n">
-        <v>12578.82</v>
+        <v>594562.67</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8120,25 +8124,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>598.3056269558823</v>
+        <v>5118.2854</v>
       </c>
       <c r="I119" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8150,32 +8154,32 @@
         <v>24</v>
       </c>
       <c r="M119" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O119" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>28012.91</v>
+        <v>120811.9</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8185,25 +8189,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>1960.237563966397</v>
+        <v>2119.874127397059</v>
       </c>
       <c r="I120" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8215,32 +8219,32 @@
         <v>24</v>
       </c>
       <c r="M120" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="N120" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P120" t="n">
-        <v>230737.81</v>
+        <v>88079.16</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8250,25 +8254,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>612.8989974</v>
+        <v>2165.574481998618</v>
       </c>
       <c r="I121" t="n">
-        <v>164</v>
+        <v>771</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8280,32 +8284,32 @@
         <v>24</v>
       </c>
       <c r="M121" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="N121" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="O121" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="P121" t="n">
-        <v>143139.02</v>
+        <v>2689541.22</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8315,25 +8319,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>920.65253652</v>
+        <v>5836.846399999999</v>
       </c>
       <c r="I122" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8345,32 +8349,32 @@
         <v>24</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N122" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>77045.64999999999</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA76723</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8380,25 +8384,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AM-C20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>3065.101673616</v>
+        <v>1235.473403164659</v>
       </c>
       <c r="I123" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8410,32 +8414,32 @@
         <v>24</v>
       </c>
       <c r="M123" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P123" t="n">
-        <v>63618.84</v>
+        <v>4669.47</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8445,25 +8449,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>912.8282939999998</v>
+        <v>2803.686903</v>
       </c>
       <c r="I124" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8475,7 +8479,7 @@
         <v>24</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -8483,24 +8487,22 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>22424.73</v>
-      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8510,25 +8512,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>4042.525302</v>
+        <v>2263.0394</v>
       </c>
       <c r="I125" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8543,29 +8545,29 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>115246.23</v>
+        <v>39426.9</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8575,25 +8577,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>708</v>
+        <v>4277.252577599999</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8605,32 +8607,32 @@
         <v>24</v>
       </c>
       <c r="M126" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O126" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>1918.37</v>
+        <v>14680.56</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8640,25 +8642,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>3103.426797881559</v>
+        <v>477.9615959999999</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8670,32 +8672,32 @@
         <v>24</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>216033.7</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8705,25 +8707,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>06 channels Mixer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>1305.459898830882</v>
+        <v>3998.590893</v>
       </c>
       <c r="I128" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8735,32 +8737,32 @@
         <v>24</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>14911.51</v>
+        <v>68163.60000000001</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8770,25 +8772,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>280.0829144294117</v>
+        <v>2280.5034</v>
       </c>
       <c r="I129" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8800,32 +8802,32 @@
         <v>24</v>
       </c>
       <c r="M129" t="n">
-        <v>314</v>
+        <v>6</v>
       </c>
       <c r="N129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="P129" t="n">
-        <v>48056.39</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8835,25 +8837,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Single UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>2311.522194589411</v>
+        <v>1825.656588</v>
       </c>
       <c r="I130" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -8865,32 +8867,32 @@
         <v>24</v>
       </c>
       <c r="M130" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>78397.17</v>
+        <v>35230.28</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8900,7 +8902,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8910,15 +8912,15 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>UB-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>4986.467599999999</v>
+        <v>9527.5088</v>
       </c>
       <c r="I131" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8930,32 +8932,32 @@
         <v>24</v>
       </c>
       <c r="M131" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
-        <v>284412.39</v>
+        <v>58031.42</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8965,25 +8967,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>XLR Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>4119.760313999999</v>
+        <v>734.122339149</v>
       </c>
       <c r="I132" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8995,32 +8997,32 @@
         <v>24</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O132" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P132" t="n">
-        <v>79701.3</v>
+        <v>59819.5</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9030,25 +9032,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>1194.50102472</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I133" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -9060,32 +9062,32 @@
         <v>24</v>
       </c>
       <c r="M133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>73812.85000000001</v>
+        <v>12578.82</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA76727</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9095,25 +9097,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-C24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>521.6161679999999</v>
+        <v>1676.644024574118</v>
       </c>
       <c r="I134" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9128,29 +9130,29 @@
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>18901.43</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9160,25 +9162,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>XLR Dynamic Mic</t>
+          <t>Wireless Mic with Charging Case</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>2173.4007</v>
+        <v>11761.9332</v>
       </c>
       <c r="I135" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9193,29 +9195,29 @@
         <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>65555</v>
+        <v>6031.48</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9225,7 +9227,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9235,15 +9237,15 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>2738.484882</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I136" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9255,32 +9257,32 @@
         <v>24</v>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>124127.54</v>
+        <v>10805.67</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9290,25 +9292,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>3748.5845172</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I137" t="n">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -9320,32 +9322,32 @@
         <v>24</v>
       </c>
       <c r="M137" t="n">
-        <v>177</v>
+        <v>11</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P137" t="n">
-        <v>1245257.21</v>
+        <v>70466.07000000001</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9355,25 +9357,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Quad UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>905.00405148</v>
+        <v>6259.394015999999</v>
       </c>
       <c r="I138" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -9385,32 +9387,32 @@
         <v>24</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>65997.42999999999</v>
+        <v>118505.16</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9420,25 +9422,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>1693.3496544</v>
+        <v>874.2436631991176</v>
       </c>
       <c r="I139" t="n">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9450,32 +9452,32 @@
         <v>24</v>
       </c>
       <c r="M139" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="N139" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O139" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P139" t="n">
-        <v>60217.88</v>
+        <v>201202.71</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA77010</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9485,25 +9487,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AI-04 Black</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>1475.964687829412</v>
+        <v>2426.920291998617</v>
       </c>
       <c r="I140" t="n">
-        <v>1355</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9515,32 +9517,30 @@
         <v>24</v>
       </c>
       <c r="M140" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>142</v>
-      </c>
-      <c r="P140" t="n">
-        <v>2559448.84</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>2803.686903</v>
+        <v>2857.758705882353</v>
       </c>
       <c r="I141" t="n">
         <v>1</v>
@@ -9580,7 +9580,7 @@
         <v>24</v>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -9589,23 +9589,23 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2460.51</v>
+        <v>1885.92</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9615,22 +9615,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>1828.2802</v>
+        <v>3103.426797881559</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -9645,20 +9645,20 @@
         <v>24</v>
       </c>
       <c r="M142" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
